--- a/storage/app/repository/NIS2.de.xlsx
+++ b/storage/app/repository/NIS2.de.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orth/NX-PrivatKL/Projekte/Docker_Experimente/DemingISMS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D338FD18-2650-044D-8547-F48C23B94903}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="31520" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,331 +25,435 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>ChatGPT</author>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/28_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/33_BSIG.htm
 https://www.buzer.de/59_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Sources:
-https://www.recht.bund.de/bgbl/1/2025/301/VO
-https://www.buzer.de/38_BSIG.htm
-https://www.buzer.de/30_BSIG.htm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.recht.bund.de/bgbl/1/2025/301/VO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.buzer.de/38_BSIG.htm
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.buzer.de/30_BSIG.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/38_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Sources:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.recht.bund.de/bgbl/1/2025/301/VO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.buzer.de/30_BSIG.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Sources:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.recht.bund.de/bgbl/1/2025/301/VO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.buzer.de/30_BSIG.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Sources:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.recht.bund.de/bgbl/1/2025/301/VO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.buzer.de/30_BSIG.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
-https://www.recht.bund.de/bgbl/1/2025/301/VO
-https://www.buzer.de/30_BSIG.htm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
-https://www.recht.bund.de/bgbl/1/2025/301/VO
-https://www.buzer.de/30_BSIG.htm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
-https://www.recht.bund.de/bgbl/1/2025/301/VO
-https://www.buzer.de/30_BSIG.htm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/30_BSIG.htm
 https://www.buzer.de/56_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Sources:
-https://www.recht.bund.de/bgbl/1/2025/301/VO
-https://www.buzer.de/32_BSIG.htm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D24" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.recht.bund.de/bgbl/1/2025/301/VO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.buzer.de/32_BSIG.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/32_BSIG.htm
 https://www.buzer.de/35_BSIG.htm
@@ -352,59 +461,106 @@
         </r>
       </text>
     </comment>
-    <comment ref="D25" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+    <comment ref="D25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/13_BSIG.htm
 https://www.buzer.de/3_BSIG.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Sources:
-https://www.recht.bund.de/bgbl/1/2025/301/VO
-https://www.buzer.de/15_BSIG.htm
-https://www.buzer.de/3_BSIG.htm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.recht.bund.de/bgbl/1/2025/301/VO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.buzer.de/15_BSIG.htm
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.buzer.de/3_BSIG.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Sources:
-https://www.recht.bund.de/bgbl/1/2025/301/VO
-https://www.buzer.de/6_BSIG.htm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D28" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sources:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.recht.bund.de/bgbl/1/2025/301/VO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.buzer.de/6_BSIG.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sources:
 https://www.recht.bund.de/bgbl/1/2025/301/VO
 https://www.buzer.de/62_BSIG.htm
 https://www.buzer.de/30_BSIG.htm
@@ -419,98 +575,98 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="167">
-  <si>
-    <t xml:space="preserve">Rahmenwerk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bereich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bereich - Beschreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abschnitt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bezeichnung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nachweise/Eingaben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bewertungsmodell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indikator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maßnahmenplan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anwendungsbereich &amp; Geltungsbereich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anwendbarkeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dieses Regelwerk richtet sich an besonders wichtige Einrichtungen und wichtige Einrichtungen im Sinne des BSI-Gesetzes (BSIG) § 28 (Sektoren/Einrichtungsarten nach Anlagen 1 und 2) sowie – soweit einschlägig – an Einrichtungen der Bundesverwaltung (§ 29). Ob eine Organisation erfasst ist, ergibt sich aus Sektor, Einrichtungsart und ggf. Größen/Schwellenwerten.
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="168">
+  <si>
+    <t>Rahmenwerk</t>
+  </si>
+  <si>
+    <t>Bereich</t>
+  </si>
+  <si>
+    <t>Bereich - Beschreibung</t>
+  </si>
+  <si>
+    <t>Abschnitt</t>
+  </si>
+  <si>
+    <t>Bezeichnung</t>
+  </si>
+  <si>
+    <t>Beschreibung</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Nachweise/Eingaben</t>
+  </si>
+  <si>
+    <t>Bewertungsmodell</t>
+  </si>
+  <si>
+    <t>Indikator</t>
+  </si>
+  <si>
+    <t>Maßnahmenplan</t>
+  </si>
+  <si>
+    <t>NIS2</t>
+  </si>
+  <si>
+    <t>Anwendungsbereich &amp; Geltungsbereich</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Anwendbarkeit</t>
+  </si>
+  <si>
+    <t>Dieses Regelwerk richtet sich an besonders wichtige Einrichtungen und wichtige Einrichtungen im Sinne des BSI-Gesetzes (BSIG) § 28 (Sektoren/Einrichtungsarten nach Anlagen 1 und 2) sowie – soweit einschlägig – an Einrichtungen der Bundesverwaltung (§ 29). Ob eine Organisation erfasst ist, ergibt sich aus Sektor, Einrichtungsart und ggf. Größen/Schwellenwerten.
 DE: BSIG §28 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Applicability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nachweis über NIS-2-Betroffenheit. Der Nachweis kann über eine Wirtschaftskanzlei oder einen Anwalt erfolgen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Einrichtung ist geprüft, ob sie unter NIS 2 fällt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grün: NIS 2 Betroffenheit verbrieft festgestellt
+    <t>#Applicability</t>
+  </si>
+  <si>
+    <t>Nachweis über NIS-2-Betroffenheit. Der Nachweis kann über eine Wirtschaftskanzlei oder einen Anwalt erfolgen.</t>
+  </si>
+  <si>
+    <t>Die Einrichtung ist geprüft, ob sie unter NIS 2 fällt</t>
+  </si>
+  <si>
+    <t>Grün: NIS 2 Betroffenheit verbrieft festgestellt
 Orange: NIS 2 Betroffenheit noch nicht bestätigt
 Rot: NIS 2 Prüfung steht noch aus</t>
   </si>
   <si>
-    <t xml:space="preserve">Prüfung aller Einrichtungskategorien in Anlage 1 und Anlage 2 des Umsetzungsgesetzes. Die Tabellen weichen von der NIS2 ab.
+    <t>Prüfung aller Einrichtungskategorien in Anlage 1 und Anlage 2 des Umsetzungsgesetzes. Die Tabellen weichen von der NIS2 ab.
 Fällt man in die Kategorie, ist man betroffen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Registrierung &amp; Informationen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unternehmensregistrierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Besonders wichtige Einrichtungen, wichtige Einrichtungen sowie Domain-Name-Registry-Diensteanbieter müssen sich spätestens drei Monate nach erstmaliger oder erneuter Einstufung beim BSI registrieren. Zu übermitteln sind u. a. Name (inkl. Rechtsform und ggf. Handelsregisternummer), Anschrift und aktuelle Kontaktdaten (inkl. E-Mail-Adresse, öffentliche IP-Adressbereiche und Telefonnummern), relevanter Sektor/Branche, EU-Mitgliedstaaten der Leistungserbringung sowie zuständige Aufsichtsbehörden. Änderungen sind fristgerecht zu melden.
+    <t>Registrierung &amp; Informationen</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Unternehmensregistrierung</t>
+  </si>
+  <si>
+    <t>Besonders wichtige Einrichtungen, wichtige Einrichtungen sowie Domain-Name-Registry-Diensteanbieter müssen sich spätestens drei Monate nach erstmaliger oder erneuter Einstufung beim BSI registrieren. Zu übermitteln sind u. a. Name (inkl. Rechtsform und ggf. Handelsregisternummer), Anschrift und aktuelle Kontaktdaten (inkl. E-Mail-Adresse, öffentliche IP-Adressbereiche und Telefonnummern), relevanter Sektor/Branche, EU-Mitgliedstaaten der Leistungserbringung sowie zuständige Aufsichtsbehörden. Änderungen sind fristgerecht zu melden.
 DE: BSIG §33 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Unternehmensregistrierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registrierungsübermittlung, Nachweise zur Einstufung der Einrichtung (Sektor/Größe), Kontaktdaten, IP-Bereiche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alle Daten sind übermittelt und von der Behörde bestätigt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grün: Daten übermittelt und bestätigt
+    <t>#Unternehmensregistrierung</t>
+  </si>
+  <si>
+    <t>Registrierungsübermittlung, Nachweise zur Einstufung der Einrichtung (Sektor/Größe), Kontaktdaten, IP-Bereiche</t>
+  </si>
+  <si>
+    <t>Alle Daten sind übermittelt und von der Behörde bestätigt.</t>
+  </si>
+  <si>
+    <t>Grün: Daten übermittelt und bestätigt
 Orange: Daten übermittelt – Bestätigung steht noch aus
 Rot: Daten nicht übermittelt</t>
   </si>
@@ -521,84 +677,84 @@
 https://www.bsi.bund.de/DE/Themen/Regulierte-Wirtschaft/NIS-2-regulierte-Unternehmen/NIS-2-Pflichten/nis-2-pflichten_node.html </t>
   </si>
   <si>
-    <t xml:space="preserve">Governance &amp; Führung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Führung / Management-Verantwortung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geschäftsleitungen besonders wichtiger Einrichtungen und wichtiger Einrichtungen sind verpflichtet, die nach BSIG § 30 erforderlichen Risikomanagementmaßnahmen umzusetzen und deren Umsetzung zu überwachen. Bei Pflichtverletzung können sie nach BSIG § 38 haftungsrechtlich in Anspruch genommen werden.
+    <t>Governance &amp; Führung</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Führung / Management-Verantwortung</t>
+  </si>
+  <si>
+    <t>Geschäftsleitungen besonders wichtiger Einrichtungen und wichtiger Einrichtungen sind verpflichtet, die nach BSIG § 30 erforderlichen Risikomanagementmaßnahmen umzusetzen und deren Umsetzung zu überwachen. Bei Pflichtverletzung können sie nach BSIG § 38 haftungsrechtlich in Anspruch genommen werden.
 DE: BSIG §38, §30 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Führung #Management_Verpflichtung ISO 27001/27002: Basic requirement for an ISMS in general; Kapitel 5 Führung; Kapitel 6 Planung / 6.1; Kapitel 8 Funktion; Kapitel 9 Managementbewertung; Kapitel 10 Kontinuierliche Verbesserung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Von der Leitung genehmigte Richtlinien, ISMS-Geltungsbereich, Protokolle aus Management-Reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Das Verfahren existiert, entspricht Best Practices, ist aktuell und wird angewendet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grün: konform
+    <t>#Führung #Management_Verpflichtung ISO 27001/27002: Basic requirement for an ISMS in general; Kapitel 5 Führung; Kapitel 6 Planung / 6.1; Kapitel 8 Funktion; Kapitel 9 Managementbewertung; Kapitel 10 Kontinuierliche Verbesserung</t>
+  </si>
+  <si>
+    <t>Von der Leitung genehmigte Richtlinien, ISMS-Geltungsbereich, Protokolle aus Management-Reviews</t>
+  </si>
+  <si>
+    <t>Das Verfahren existiert, entspricht Best Practices, ist aktuell und wird angewendet.</t>
+  </si>
+  <si>
+    <t>Grün: konform
 Orange: geringfügige Nichtkonformität
 Rot: wesentliche Nichtkonformität</t>
   </si>
   <si>
-    <t xml:space="preserve">Ergebnisse der Untersuchungen und Risikoprüfungen, z.B. externe Pentests, müssen aktiv betrachtet und entsprechend der Empfehlungen umgesetzt werden. Ggf. kann das auch das Abschalten von Systemen beinhalten.
+    <t>Ergebnisse der Untersuchungen und Risikoprüfungen, z.B. externe Pentests, müssen aktiv betrachtet und entsprechend der Empfehlungen umgesetzt werden. Ggf. kann das auch das Abschalten von Systemen beinhalten.
 Es müssen ausreichend Ressourcen bereitgestellt werden. Dabei ist daran zu denken, dass die Maßnahmen nicht nur einmalige, sondern auch wiederkehrende Betreuung benötigen.</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schulung und Sensibilisierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Geschäftsleitungen besonders wichtiger Einrichtungen und wichtiger Einrichtungen müssen regelmäßig an Schulungen teilnehmen, um ausreichende Kenntnisse und Fähigkeiten zur Erkennung und Bewertung von Risiken sowie von Risikomanagementpraktiken im Bereich der Sicherheit in der Informationstechnik zu erlangen und die Auswirkungen auf die von der Einrichtung erbrachten Dienste beurteilen zu können.
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Schulung und Sensibilisierung</t>
+  </si>
+  <si>
+    <t>Die Geschäftsleitungen besonders wichtiger Einrichtungen und wichtiger Einrichtungen müssen regelmäßig an Schulungen teilnehmen, um ausreichende Kenntnisse und Fähigkeiten zur Erkennung und Bewertung von Risiken sowie von Risikomanagementpraktiken im Bereich der Sicherheit in der Informationstechnik zu erlangen und die Auswirkungen auf die von der Einrichtung erbrachten Dienste beurteilen zu können.
 DE: BSIG §38 Abs. 3 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Schulung_und_Sensibilisierung ISO 27001/27002: Kapitel 7.2 Kompetenz; Kapitel 7.3 Sensibilisierung; A.6.3 Sensibilisierung, Ausbildung und Schulung zur Informationssicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protokolle aus Management-Reviews, Schulungsnachweise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schulungen der Geschäftsleitung sind durchgeführt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grün: Schulungen durchgeführt
+    <t>#Schulung_und_Sensibilisierung ISO 27001/27002: Kapitel 7.2 Kompetenz; Kapitel 7.3 Sensibilisierung; A.6.3 Sensibilisierung, Ausbildung und Schulung zur Informationssicherheit</t>
+  </si>
+  <si>
+    <t>Protokolle aus Management-Reviews, Schulungsnachweise</t>
+  </si>
+  <si>
+    <t>Schulungen der Geschäftsleitung sind durchgeführt</t>
+  </si>
+  <si>
+    <t>Grün: Schulungen durchgeführt
 Orange: Schulungen sind geplant
 Rot: Schulungen sind nicht geplant und nicht durchgeführt</t>
   </si>
   <si>
-    <t xml:space="preserve">Dokumentierte Schulung der Geschäftsleitung
+    <t>Dokumentierte Schulung der Geschäftsleitung
 regelmäßige Cyber-Security-Awareness-Angebote an die Mitarbeiter, damit die Risiken im eigenen Unternehmen, die ermittelt wurden, auch bekannt sind
 Nutzung der Unterlagen und Hilfen von der Allianz für Cybersicherheit und des BSI 
 Über die eigene Cyberversicherung gibt es regelmäßig Zugriff auf Schulungsmaterial</t>
   </si>
   <si>
-    <t xml:space="preserve">Cybersicherheits-Risikomanagementmaßnahmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISMS, risikobasierter Ansatz, Stand der Technik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es sind geeignete, verhältnismäßige und wirksame technische und organisatorische Maßnahmen zu ergreifen, um Störungen der Verfügbarkeit, Integrität und Vertraulichkeit der für die Erbringung der Dienste genutzten IT-Systeme, Komponenten und Prozesse zu vermeiden und die Auswirkungen von Sicherheitsvorfällen möglichst gering zu halten. Die Maßnahmen sollen dem Stand der Technik entsprechen, einschlägige europäische und internationale Normen berücksichtigen und auf einem gefahrenübergreifenden Ansatz beruhen; die Einhaltung ist zu dokumentieren.
+    <t>Cybersicherheits-Risikomanagementmaßnahmen</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>ISMS, risikobasierter Ansatz, Stand der Technik</t>
+  </si>
+  <si>
+    <t>Es sind geeignete, verhältnismäßige und wirksame technische und organisatorische Maßnahmen zu ergreifen, um Störungen der Verfügbarkeit, Integrität und Vertraulichkeit der für die Erbringung der Dienste genutzten IT-Systeme, Komponenten und Prozesse zu vermeiden und die Auswirkungen von Sicherheitsvorfällen möglichst gering zu halten. Die Maßnahmen sollen dem Stand der Technik entsprechen, einschlägige europäische und internationale Normen berücksichtigen und auf einem gefahrenübergreifenden Ansatz beruhen; die Einhaltung ist zu dokumentieren.
 DE: BSIG §30 Abs. 1–2 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#ISMS #risikobasierter_Ansatz #Stand_der_Technik ISO 27001/27002: Kapitel 4 Kontext der Organisation; Kapitel 6 Planung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risikobewertungsberichte, ISMS-Dokumentation, SoA (Statement of Applicability), Audits, Risikobehandlungspläne</t>
+    <t>#ISMS #risikobasierter_Ansatz #Stand_der_Technik ISO 27001/27002: Kapitel 4 Kontext der Organisation; Kapitel 6 Planung</t>
+  </si>
+  <si>
+    <t>Risikobewertungsberichte, ISMS-Dokumentation, SoA (Statement of Applicability), Audits, Risikobehandlungspläne</t>
   </si>
   <si>
     <t xml:space="preserve">kontinuierliche Marktanalyse hinsichtlich der eigenen Systeme und Applikationen sowie Pflegen einer Übersicht der eingesetzten Anwendungen und deren Versionen, verbunden mit dem Supportzustand:
@@ -608,46 +764,46 @@
 Empfehlung für Nachweise: Als Basis können Checklisten o.ä., die bereits Risikobetrachtungen enthalten, genutzt werden oder Leitfäden bzw. Standards zur Umsetzung eines individuellen Risikomanagements. Für eine kontinuierliche Betrachtung sollte ein geeigneter lokaler Partner einbezogen werden (z.B. das IT Systemhaus mit speziellem NIS-2-Wissen). </t>
   </si>
   <si>
-    <t xml:space="preserve">Best Practice / Standards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allgemeiner Verweis auf ISO/IEC-27000-Reihe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bei der Ausgestaltung der Risikomanagementmaßnahmen sollen einschlägige europäische und internationale Normen berücksichtigt werden. Als Orientierung können insbesondere ISO/IEC 27001 und die ISO/IEC-27000-Reihe (z. B. ISO/IEC 27002) herangezogen werden.
+    <t>Best Practice / Standards</t>
+  </si>
+  <si>
+    <t>3.2.1</t>
+  </si>
+  <si>
+    <t>Allgemeiner Verweis auf ISO/IEC-27000-Reihe</t>
+  </si>
+  <si>
+    <t>Bei der Ausgestaltung der Risikomanagementmaßnahmen sollen einschlägige europäische und internationale Normen berücksichtigt werden. Als Orientierung können insbesondere ISO/IEC 27001 und die ISO/IEC-27000-Reihe (z. B. ISO/IEC 27002) herangezogen werden.
 DE: BSIG §30 Abs. 2 Satz 1 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Allgemeiner_ISO_Verweis #IEC_27000_Reihe ISO 27001/27002: Alle Kontrollen in Bezug auf die genannten Bedrohungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richtlinien, Verfahren, Aufzeichnungen und Protokolle (Logs) als Nachweis für Umsetzung und Betrieb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standards/Kataloge mit dem Bezug zum Allgefahrenansatz nutzen, hier kann ISO 27001, BSI-Grundschutz und TISAX genutzt werden.
+    <t>#Allgemeiner_ISO_Verweis #IEC_27000_Reihe ISO 27001/27002: Alle Kontrollen in Bezug auf die genannten Bedrohungen</t>
+  </si>
+  <si>
+    <t>Richtlinien, Verfahren, Aufzeichnungen und Protokolle (Logs) als Nachweis für Umsetzung und Betrieb</t>
+  </si>
+  <si>
+    <t>Standards/Kataloge mit dem Bezug zum Allgefahrenansatz nutzen, hier kann ISO 27001, BSI-Grundschutz und TISAX genutzt werden.
 Für Betriebssicherheit die TRBS 115-1 beachten: https://www.baua.de/DE/Angebote/Regelwerk/TRBS/TRBS-1115-Teil-1.html, 
 KMU-gerecht sind unter anderem
 VDS 1000: https://www.kiss-nis2.de/doku.php
 Grundschutz Plus: https://security4kmu.de/</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richtlinien zur Risikoanalyse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richtlinien zur Risikoanalyse und zur Sicherheit von Informationssystemen
+    <t>3.2.2</t>
+  </si>
+  <si>
+    <t>Richtlinien zur Risikoanalyse</t>
+  </si>
+  <si>
+    <t>Richtlinien zur Risikoanalyse und zur Sicherheit von Informationssystemen
 DE: BSIG §30 Abs. 2 Satz 2 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Richtlinien #Risikomanagement ISO 27001/27002: Kapitel 5 Führung; Kapitel 6 Planung; A.5.1 Richtlinien zur Informationssicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prüfen, welchem Ansatz man grundsätzlich folgen möchte, Dokumentation und Begründung der Entscheidung auf Basis von:
+    <t>#Richtlinien #Risikomanagement ISO 27001/27002: Kapitel 5 Führung; Kapitel 6 Planung; A.5.1 Richtlinien zur Informationssicherheit</t>
+  </si>
+  <si>
+    <t>Prüfen, welchem Ansatz man grundsätzlich folgen möchte, Dokumentation und Begründung der Entscheidung auf Basis von:
 * Ausmaß der Risikoexposition 
 * die Größe des Unternehmens
 * die Eintrittswahrscheinlichkeit
@@ -656,41 +812,41 @@
 Es ist zu erwarten, dass Kunden nach dem NIS 2 Risikokonzept anfragen. Eine vorgefertigte Antwort sollte hierzu parat liegen. Anfragen sind zu erwarten seitens Sales, IT-Betrieb, Wartung/Instandhaltung für z.B. Rechte-/Rollenkonzept, Zugriffsschutz, Fernwartung, etc.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Management von Sicherheitsvorfällen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Behandlung von Sicherheitsvorfällen
+    <t>3.2.3</t>
+  </si>
+  <si>
+    <t>Management von Sicherheitsvorfällen</t>
+  </si>
+  <si>
+    <t>Behandlung von Sicherheitsvorfällen
 DE: BSIG §30 Abs. 2 Satz 2  (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Vorfallmanagement ISO 27001/27002: A.5.24 Informationssicherheitsvorfallmanagement; A.5.26 Reaktion auf Informationssicherheitsvorfälle; A.5.27 Aus Informationssicherheitsvorfällen lernen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übung der Einordnung von Vorfällen (Störung, Krise, Security-Vorfall) auf Basis z.B. Cyber-Sicherheitsnetzwerk des BSI
+    <t>#Vorfallmanagement ISO 27001/27002: A.5.24 Informationssicherheitsvorfallmanagement; A.5.26 Reaktion auf Informationssicherheitsvorfälle; A.5.27 Aus Informationssicherheitsvorfällen lernen</t>
+  </si>
+  <si>
+    <t>Übung der Einordnung von Vorfällen (Störung, Krise, Security-Vorfall) auf Basis z.B. Cyber-Sicherheitsnetzwerk des BSI
 Übung der Ermittlung von erheblichen Sicherheitsvorfällen, z.B. mit Use Cases, Tabletop-Übungen
 Dokumentierung der Meldewege, Kontakte auch offline, um Zugriff darauf zu erhalten, wenn die Systeme nicht verfügbar sind.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business-Continuity-Management (BCM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business-Continuity, z. B. Backup-Management und Disaster Recovery, sowie Krisenmanagement
+    <t>3.2.4</t>
+  </si>
+  <si>
+    <t>Business-Continuity-Management (BCM)</t>
+  </si>
+  <si>
+    <t>Business-Continuity, z. B. Backup-Management und Disaster Recovery, sowie Krisenmanagement
 DE: BSIG §30 Abs. 2 Satz 3 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Business_Continuity_Management ISO 27001/27002: A.5.29 Informationssicherheit während einer Störung; A.5.30 IKT-Bereitschaft für Geschäftskontinuität; A.8.13 Sichern von Informationen; A.8.14 Redundanz der Informationsverarbeitungsmittel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risikobewertungsberichte, ISMS-Dokumentation, SoA (Statement of Applicability), Audits, Risikobehandlungspläne, Backup-Pläne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erarbeitung eines Backupkonzepts für relevante IT-Systeme, insbesondere Finanzbuchhaltung, Produktionsdaten, Konstruktionsdaten
+    <t>#Business_Continuity_Management ISO 27001/27002: A.5.29 Informationssicherheit während einer Störung; A.5.30 IKT-Bereitschaft für Geschäftskontinuität; A.8.13 Sichern von Informationen; A.8.14 Redundanz der Informationsverarbeitungsmittel</t>
+  </si>
+  <si>
+    <t>Risikobewertungsberichte, ISMS-Dokumentation, SoA (Statement of Applicability), Audits, Risikobehandlungspläne, Backup-Pläne</t>
+  </si>
+  <si>
+    <t>Erarbeitung eines Backupkonzepts für relevante IT-Systeme, insbesondere Finanzbuchhaltung, Produktionsdaten, Konstruktionsdaten
 Backup von Cloud-only Systemen bei Dienstleistern nicht als gegeben annehmen - Zugriff auf ein Backup muss immer möglich sein.
 Prüfung, ob Redundanzen von kritischen Systemen oder Komponenten sinnvoll erscheinen.
 Erarbeitung eines Wiederherstellungsplans und Übung der Wiederherstellung bei Einrichtung (Funktionsprüfung Einzeldatenwiederherstellung, Desaster-Recovery). Regelmäßige Prüfungen durchführen und dokumentieren.
@@ -698,20 +854,20 @@
 Melde- und Auskunftspflicht bei der Notfallkommunikation mit einplanen, da Nichterreichbarkeit des Kontakts ein Bußgeld nach sich ziehen kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lieferkettensicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Lieferkette ist abzusichern; hierzu gehören sicherheitsbezogene Aspekte der Beziehungen zu unmittelbaren Anbietern oder Diensteanbietern (z. B. Auswahlkriterien, vertragliche Mindestanforderungen, Überwachung sowie Incident-Kommunikation).
+    <t>3.2.5</t>
+  </si>
+  <si>
+    <t>Lieferkettensicherheit</t>
+  </si>
+  <si>
+    <t>Die Lieferkette ist abzusichern; hierzu gehören sicherheitsbezogene Aspekte der Beziehungen zu unmittelbaren Anbietern oder Diensteanbietern (z. B. Auswahlkriterien, vertragliche Mindestanforderungen, Überwachung sowie Incident-Kommunikation).
 DE: BSIG §30 Abs. 2 Satz 4 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Lieferkettensicherheit ISO 27001/27002: #Lieferantenbeziehungen_security; A.5.19 Informationssicherheit in Lieferantenbeziehungen; A.5.20 Berücksichtigung der Informationssicherheit in Verträgen mit Lieferanten; A.5.21 Informationssicherehitsmanagment in der IKT-Lieferkette; A.5.22 Management der Lieferantenleistung; A.5.23 Informationssicherheit bei Nutzung von Cloud-Diensten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richtlinie/Prozess etablieren, der eine angemessene Lieferantenauskunft einfordert,  z.B. ISO 27001/TISAX/IEC 62443-4-1 
+    <t>#Lieferkettensicherheit ISO 27001/27002: #Lieferantenbeziehungen_security; A.5.19 Informationssicherheit in Lieferantenbeziehungen; A.5.20 Berücksichtigung der Informationssicherheit in Verträgen mit Lieferanten; A.5.21 Informationssicherehitsmanagment in der IKT-Lieferkette; A.5.22 Management der Lieferantenleistung; A.5.23 Informationssicherheit bei Nutzung von Cloud-Diensten</t>
+  </si>
+  <si>
+    <t>Richtlinie/Prozess etablieren, der eine angemessene Lieferantenauskunft einfordert,  z.B. ISO 27001/TISAX/IEC 62443-4-1 
 Als Fragebogen kann der standardisierte Fragebogen aus UP-KRITIS oder VDMA genutzt werden:
 https://vdma.eu/de/viewer/-/v2article/render/82349740 
 https://www.bsi.bund.de/SharedDocs/Downloads/DE/BSI/KRITIS/UPK/upk-anforderungen-lieferanten.html 
@@ -723,20 +879,20 @@
 Eine security.txt aus Textdatei auf der Homepage ist einfach umzusetzen und sollte daher auch bei KMU umgesetzt werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sichere Beschaffung und Entwicklung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitsmaßnahmen bei Erwerb, Entwicklung und Wartung von informationstechnischen Systemen, Komponenten und Prozessen – einschließlich Management und Offenlegung von Schwachstellen – sind festzulegen und umzusetzen.
+    <t>3.2.6</t>
+  </si>
+  <si>
+    <t>Sichere Beschaffung und Entwicklung</t>
+  </si>
+  <si>
+    <t>Sicherheitsmaßnahmen bei Erwerb, Entwicklung und Wartung von informationstechnischen Systemen, Komponenten und Prozessen – einschließlich Management und Offenlegung von Schwachstellen – sind festzulegen und umzusetzen.
 DE: BSIG §30 Abs. 2 Satz 5 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Sichere_Entwicklung ISO 27001/27002: A.5.7 Bedrohungsinformationen; A.5.6 Beziehungen zu spezialisierten Arbeitsgruppen; A.8.25 Sicherer Entwicklungszyklus; A.8.26 Anforderung an die Anwendungssicherheit; A.8.27 Prinzipen der sicheren Systemarchitektur und Entwicklung; A.8.28 Sichere Programmierung; A.8.29 Sicherheitstests in Entwicklung und Abnahme; A.8.30 Ausgelagerte Entwicklung; A.8.31 Trennung von Entwicklungs-, Test- und Produktionsumgebungen; A.8.32 Änderungsmanagement; A.8.33 Testdaten; A.8.34 Schutz von Informationssystemen während Audits und Tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es sollte eine konkrete Auskunft zum End of Support (EOS) eingefordert werden. Beschaffungsrichtlinie für IT/OT-Systeme mit Blick auf Cyber-Security.
+    <t>#Sichere_Entwicklung ISO 27001/27002: A.5.7 Bedrohungsinformationen; A.5.6 Beziehungen zu spezialisierten Arbeitsgruppen; A.8.25 Sicherer Entwicklungszyklus; A.8.26 Anforderung an die Anwendungssicherheit; A.8.27 Prinzipen der sicheren Systemarchitektur und Entwicklung; A.8.28 Sichere Programmierung; A.8.29 Sicherheitstests in Entwicklung und Abnahme; A.8.30 Ausgelagerte Entwicklung; A.8.31 Trennung von Entwicklungs-, Test- und Produktionsumgebungen; A.8.32 Änderungsmanagement; A.8.33 Testdaten; A.8.34 Schutz von Informationssystemen während Audits und Tests</t>
+  </si>
+  <si>
+    <t>Es sollte eine konkrete Auskunft zum End of Support (EOS) eingefordert werden. Beschaffungsrichtlinie für IT/OT-Systeme mit Blick auf Cyber-Security.
 Entscheidungen für Systeme/Lösungen sollte bei den Prozessverantwortlichen verbleiben, die zentrale Security-Vorgaben beachten müssen.
 Etablierung eines Secure-Gateways für externe Zugriffe, über das der Zugriff von Dienstleistern gezielt gesteuert und dokumentiert/protokolliert werden kann.
 In Ausschreibungen von IT/OT festlegen, dass das bereitgestellte Secure-Gateway vom Dienstleister genutzt werden muss.
@@ -744,36 +900,36 @@
 Vor Inbetriebnahme sollte (Im Idealfall) ein Wirksamkeitstest durchgeführt werden (SAT, FAT) um den Stand der Technik zu dokumentieren. Das Ergebnis sollte in etwa mit dem Ergebnis des Lieferantenscans übereinstimmen.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risikomanagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richtlinien und Verfahren zur Bewertung der Wirksamkeit der Cybersicherheits-Risikomanagementmaßnahmen
+    <t>3.2.7</t>
+  </si>
+  <si>
+    <t>Risikomanagement</t>
+  </si>
+  <si>
+    <t>Richtlinien und Verfahren zur Bewertung der Wirksamkeit der Cybersicherheits-Risikomanagementmaßnahmen
 DE: BSIG §30 Abs. 2 Satz 6 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Risikomanagement ISO 27001/27002: Kapitel 9 Bewertung der Leistung; A.5.35 Unabhängige Überprüfung der Informationssicherheit; A.5.36 Einhaltung von Richtlinien und Standards zur Informationssicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPI's zur kontrollierten und standardisierten Vorgehensweise bilden, z.B. Anteil der geschulten Mitarbeiter, Passwortqualität, offene (kritische) Tickets, Anzahl Schwachstellen, Anzahl der erfolgreich wiederhergestellten Dateien aus dem Backup, Anzahl der erfolgreich wiederhergestellten Servern aus dem Backup etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grundlegende Schulungen und Sensibilisierungsmaßnahmen im Bereich der Sicherheit in der Informationstechnik sind durchzuführen und regelmäßig zu aktualisieren.
+    <t>#Risikomanagement ISO 27001/27002: Kapitel 9 Bewertung der Leistung; A.5.35 Unabhängige Überprüfung der Informationssicherheit; A.5.36 Einhaltung von Richtlinien und Standards zur Informationssicherheit</t>
+  </si>
+  <si>
+    <t>KPI's zur kontrollierten und standardisierten Vorgehensweise bilden, z.B. Anteil der geschulten Mitarbeiter, Passwortqualität, offene (kritische) Tickets, Anzahl Schwachstellen, Anzahl der erfolgreich wiederhergestellten Dateien aus dem Backup, Anzahl der erfolgreich wiederhergestellten Servern aus dem Backup etc.</t>
+  </si>
+  <si>
+    <t>3.2.8</t>
+  </si>
+  <si>
+    <t>Grundlegende Schulungen und Sensibilisierungsmaßnahmen im Bereich der Sicherheit in der Informationstechnik sind durchzuführen und regelmäßig zu aktualisieren.
 DE: BSIG §30 Abs. 2 Nr. 7 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Schulung_und_Sensibilisierung ISO 27001/27002: A.6.3 Sensibilisierung, Ausbildung und Schulung zur Informationssicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risikobewertungsberichte, ISMS-Dokumentation, SoA (Statement of Applicability), Audits, Risikobehandlungspläne, Schulungspläne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementation und Dokumentation der Basismaßnahmen
+    <t>#Schulung_und_Sensibilisierung ISO 27001/27002: A.6.3 Sensibilisierung, Ausbildung und Schulung zur Informationssicherheit</t>
+  </si>
+  <si>
+    <t>Risikobewertungsberichte, ISMS-Dokumentation, SoA (Statement of Applicability), Audits, Risikobehandlungspläne, Schulungspläne</t>
+  </si>
+  <si>
+    <t>Implementation und Dokumentation der Basismaßnahmen
 * Unterbindung eines anonymen Zugriffs auf Unternehmensdaten
 * Abgestuftes Nutzerkonzept
 * Passwortrichtlinie
@@ -787,53 +943,53 @@
 Phishing-Kampagnen sind von der Geschäftsleitung zu beauftragen, vom Betriebsrat zu genehmigen und DSGVO-konform auszuführen, den DSB frühst möglichst involvieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kryptographie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richtlinien und Verfahren zum Einsatz von Kryptographie und – soweit angemessen – Verschlüsselung;
+    <t>3.2.9</t>
+  </si>
+  <si>
+    <t>Kryptographie</t>
+  </si>
+  <si>
+    <t>Richtlinien und Verfahren zum Einsatz von Kryptographie und – soweit angemessen – Verschlüsselung;
 DE: BSIG §30 Abs. 2 Nr. 8 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Kryptographie ISO 27001/27002: A.8.24 Einsatz von Kryptographie;  A.5.31 Trennung von Entwicklungs-, Test- und Produktionsumgebungen; Verschlüsselung als mögliche Maßnahme in mehreren Kontrollen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soweit möglich sollten Datenübertragungen nur mit Transportverschlüsselungen nach Stand der Technik erfolgen.
+    <t>#Kryptographie ISO 27001/27002: A.8.24 Einsatz von Kryptographie;  A.5.31 Trennung von Entwicklungs-, Test- und Produktionsumgebungen; Verschlüsselung als mögliche Maßnahme in mehreren Kontrollen</t>
+  </si>
+  <si>
+    <t>Soweit möglich sollten Datenübertragungen nur mit Transportverschlüsselungen nach Stand der Technik erfolgen.
 Veraltete kryptographische Verfahren müssen aussortiert werden (z.B. MD5, TLS 1.0, TLS1.1, SMBv1, SNMPv1,2).
 Dokumentation der eingesetzten Verfahren für ein Life-Cycle- und Security-Management</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal-/HR-Sicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheit des Personals, Zugriffskontrollrichtlinien und Asset-Management;
+    <t>3.2.10</t>
+  </si>
+  <si>
+    <t>Personal-/HR-Sicherheit</t>
+  </si>
+  <si>
+    <t>Sicherheit des Personals, Zugriffskontrollrichtlinien und Asset-Management;
 DE: BSIG §30 Abs. 2 Nr. 9 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Personal_Sicherheit ISO 27001/27002: A.6 People controls; #Personal_sicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anfordern eines Polizeilichen Führungszeugnisses bei den besonders exponierten Personenkreisen, Prüfung von Sanktionslisten, Prüfung des Lebenslaufs.
+    <t>#Personal_Sicherheit ISO 27001/27002: A.6 People controls; #Personal_sicherheit</t>
+  </si>
+  <si>
+    <t>Anfordern eines Polizeilichen Führungszeugnisses bei den besonders exponierten Personenkreisen, Prüfung von Sanktionslisten, Prüfung des Lebenslaufs.
 Vertragliche Vereinbarung/Verpflichtung der Mitarbeiter auf Security.
 Onboarding bezüglich geltender Security-Richtlinien, Sanktionierung, Durchsetzung von Maßnahmen bei Vorfällen, ggf. Offboarding bei Vertragsende.
 Gesonderte Verpflichtung bei mobilen Arbeiten (HomeOffice, Mobiltelefon) und Anmeldung an Fremdgeräten (keine Nutzung von Firmenaccounts)</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zugriffskontrolle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#Zugriffskontrolle ISO 27001/27002: A.5.15 Zugriffskontrolle; A.5.16 Identitätsverwaltungt; A.5.17 Authentifizierungsinformationen; A.5.18 Zugangsrechte; A.7.2 Physische Zugangskontrolle; #Identitäts_und_Zugriffsmanagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zugangsschutz durch verwaltete Ausweiskarten, z.B. zu einer Leitwarte, IT-Serverraum. Festlegung von physischen Sicherheitszonen, z.B. Betriebsgelände -&gt; Verwaltungsgebäude -&gt; Serverraum -&gt; Rack -&gt; USB-Schnittstelle
+    <t>3.2.11</t>
+  </si>
+  <si>
+    <t>Zugriffskontrolle</t>
+  </si>
+  <si>
+    <t>#Zugriffskontrolle ISO 27001/27002: A.5.15 Zugriffskontrolle; A.5.16 Identitätsverwaltungt; A.5.17 Authentifizierungsinformationen; A.5.18 Zugangsrechte; A.7.2 Physische Zugangskontrolle; #Identitäts_und_Zugriffsmanagement</t>
+  </si>
+  <si>
+    <t>Zugangsschutz durch verwaltete Ausweiskarten, z.B. zu einer Leitwarte, IT-Serverraum. Festlegung von physischen Sicherheitszonen, z.B. Betriebsgelände -&gt; Verwaltungsgebäude -&gt; Serverraum -&gt; Rack -&gt; USB-Schnittstelle
 Keine Adminrechte für das gesamte Personal, außer wenn dies für die Rolle notwendig ist, dies gilt auch für die Geschäftsführung sowie das mittlere Management.
 Tieriering der Administration (Single User - single Account, Anwendungen mit dedizierten Accounts ohne Anmelderechte an den Clients)
 Ggf. AD-Segmentierung für Produktionsumgebung, Priviledged Access Workstations für Administratoren
@@ -841,16 +997,16 @@
 Vermeidung einer flachen Netztopologie, Nutzung von VLANs</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset-Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#Asset_Management ISO 27001/27002: A.5.9 Inventarisierung; A.5.10 Ordnungsgemäße Verwendung von Informationen; A.5.11 Rückgabe von Vermögenswerten; A.5.12 Klassifizierung von Informationen; #Asset_Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hilfreich ist eine Auflistung aller Assets und Klassifizierung von Assets bezüglich des Wertes für das Unternehmen mit Aufrechterhaltung der Aktualität der Assetliste mindestens bei Zu/Abgängen von Assets.
+    <t>3.2.12</t>
+  </si>
+  <si>
+    <t>Asset-Management</t>
+  </si>
+  <si>
+    <t>#Asset_Management ISO 27001/27002: A.5.9 Inventarisierung; A.5.10 Ordnungsgemäße Verwendung von Informationen; A.5.11 Rückgabe von Vermögenswerten; A.5.12 Klassifizierung von Informationen; #Asset_Management</t>
+  </si>
+  <si>
+    <t>Hilfreich ist eine Auflistung aller Assets und Klassifizierung von Assets bezüglich des Wertes für das Unternehmen mit Aufrechterhaltung der Aktualität der Assetliste mindestens bei Zu/Abgängen von Assets.
 Nutzung der Inventarliste, auch Betrachtung der Unternehmensprozesse, Services, Softwareversionen
 --&gt; womit verdiene ich Geld?
 --&gt; Was ist dafür notwendig?
@@ -858,20 +1014,20 @@
 Das Asset Management kann die anderen Maßnahmen unterstützen, z.B. Schwachstellen/Patch Management</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authentifizierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verwendung von Lösungen zur Multi-Faktor-Authentifizierung oder kontinuierlichen Authentifizierungslösungen […] soweit angemessen.
+    <t>3.2.13</t>
+  </si>
+  <si>
+    <t>Authentifizierung</t>
+  </si>
+  <si>
+    <t>Verwendung von Lösungen zur Multi-Faktor-Authentifizierung oder kontinuierlichen Authentifizierungslösungen […] soweit angemessen.
 DE: BSIG §30 Abs. 2 Nr. 10 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Authentifizierung ISO 27001/27002: A.6.7 Remote-Arbeit; A.8.5 Sichere Authentifizierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M365 bzw. O365 nur mit MFA Anmeldung bei nicht gemanageten Geräten
+    <t>#Authentifizierung ISO 27001/27002: A.6.7 Remote-Arbeit; A.8.5 Sichere Authentifizierung</t>
+  </si>
+  <si>
+    <t>M365 bzw. O365 nur mit MFA Anmeldung bei nicht gemanageten Geräten
 MFA: keine Nutzung von unsicheren Zweitmöglichkeiten, z.B. "Rautetaste".
 Bei Zugriff auf Anwendungen MFA,wenn möglich verpflichtend, einrichten
 Nutzung einer zugelassenen Authenticator-App mit Leitlinie festlegen
@@ -881,129 +1037,129 @@
 Vermeidung der Speicherung von biometrischen Daten außerhalb besonders geschützter Systeme.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verwendung [… ] gesicherte Sprach-, Video- und Textkommunikation [...] soweit angemessen.
+    <t>3.2.14</t>
+  </si>
+  <si>
+    <t>Kommunikation</t>
+  </si>
+  <si>
+    <t>Verwendung [… ] gesicherte Sprach-, Video- und Textkommunikation [...] soweit angemessen.
 DE: BSIG §30 Abs. 2 Nr. 10 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Kommunikation ISO 27001/27002: 5.14 Information Transfer, A.8.20 Netzwerksicherheit, A.8.21 Sicherheit der Netzwerkdienste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telefonie auf IP-Telefonie mit Verschlüsselung umstellen, richtige Einstellungen der Videokonferenz-Systeme (organisatorische Maßnahmen), so dass Gäste nicht unkontrolliert teilnehmen können. 
+    <t>#Kommunikation ISO 27001/27002: 5.14 Information Transfer, A.8.20 Netzwerksicherheit, A.8.21 Sicherheit der Netzwerkdienste</t>
+  </si>
+  <si>
+    <t>Telefonie auf IP-Telefonie mit Verschlüsselung umstellen, richtige Einstellungen der Videokonferenz-Systeme (organisatorische Maßnahmen), so dass Gäste nicht unkontrolliert teilnehmen können. 
 Konfiguration der Systeme muss überprüft und angepasst werden. Mailserver mit aktueller Verschlüsselung der Übertragung betreiben oder in der Cloud betreiben. 
 Härtungs-Empfehlungen von Informations-Systemen umsetzen. Sowohl bei Cloud-Anbieter als bei selbst gehosteten Systemen sind Security-Einstellungen aktiv zu verwalten. 
 Leitlinie für sensible Informationen erstellen, wie diese bei der Übertragung zu sichern sind (Verschlüsselung, geeignete Kanäle (Secure Cloud))</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notfall-Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verwendung [...]  abgesicherter Notfall-Kommunikationssysteme innerhalb der Einrichtung, soweit angemessen.
+    <t>3.2.15</t>
+  </si>
+  <si>
+    <t>Notfall-Kommunikation</t>
+  </si>
+  <si>
+    <t>Verwendung [...]  abgesicherter Notfall-Kommunikationssysteme innerhalb der Einrichtung, soweit angemessen.
 DE: BSIG §30 Abs. 2 Nr. 10 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Kommunikation ISO 27001/27002: A.5.29 Informationssicherheit während einer Störung, A.5.30 IKT-Bereitschaft für Geschäftskontinuität</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notfallsystem überlegen, das bei Ausfall des Haupt-Systems genutzt werden kann, z.B. ein freies System (Jitsi, Signal). 
+    <t>#Kommunikation ISO 27001/27002: A.5.29 Informationssicherheit während einer Störung, A.5.30 IKT-Bereitschaft für Geschäftskontinuität</t>
+  </si>
+  <si>
+    <t>Notfallsystem überlegen, das bei Ausfall des Haupt-Systems genutzt werden kann, z.B. ein freies System (Jitsi, Signal). 
 Einen virtuellen Raum im Notfallhandbuch definieren, in dem sich alle Notfall-Manager treffen können.
 In der Notfallübung sollten die Systeme angemessen getestet werden. (Neue) Mitarbeiter im Notfallteam sollten sich mit dem System vertraut machen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Umgang mit Schwachstellen &amp; Offenlegung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einsatz zertifizierter Produkte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durch Rechtsverordnung kann festgelegt werden, dass bestimmte IKT-Produkte, IKT-Dienste oder IKT-Prozesse nur verwendet werden dürfen, wenn sie über eine Cybersicherheitszertifizierung gemäß europäischen Schemata nach der Verordnung (EU) 2019/881 verfügen.
+    <t>Umgang mit Schwachstellen &amp; Offenlegung</t>
+  </si>
+  <si>
+    <t>3.2.16</t>
+  </si>
+  <si>
+    <t>Einsatz zertifizierter Produkte</t>
+  </si>
+  <si>
+    <t>Durch Rechtsverordnung kann festgelegt werden, dass bestimmte IKT-Produkte, IKT-Dienste oder IKT-Prozesse nur verwendet werden dürfen, wenn sie über eine Cybersicherheitszertifizierung gemäß europäischen Schemata nach der Verordnung (EU) 2019/881 verfügen.
 DE: BSIG §30 Abs. 6, §56 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Einsatz_zertifizierter_Produkte #Zukunft #optional ISO 27001/27002: A.5.19 Informationssicherheit in Lieferantenbeziehungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richtlinie zur Schwachstellen-Offenlegung, Schwachstellenaufzeichnungen, Nachweise Patch-Management, Penetrationstestberichte, Zertifizierungen der Systeme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Entwicklung der Rechtsverordnung beobachten. Schwerpunkt liegt zur Zeit bei 5G und Software-Produkten.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meldung von Sicherheitsvorfällen &amp; Benachrichtigungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meldung/Reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erhebliche Sicherheitsvorfälle sind über die gemeinsame Meldestelle zu melden: (1) frühe Erstmeldung spätestens binnen 24 Stunden nach Kenntniserlangung, (2) Meldung spätestens binnen 72 Stunden mit Bestätigung/Aktualisierung und erster Bewertung (inkl. Schweregrad/Auswirkungen und ggf. Kompromittierungsindikatoren), (3) auf Ersuchen Zwischenmeldungen, (4) Abschlussmeldung spätestens einen Monat nach der 72-Stunden-Meldung (bei andauerndem Vorfall zunächst Fortschrittsmeldung). Die Pflichten gelten frühestens ab Einrichtung des Meldewegs.
+    <t>#Einsatz_zertifizierter_Produkte #Zukunft #optional ISO 27001/27002: A.5.19 Informationssicherheit in Lieferantenbeziehungen</t>
+  </si>
+  <si>
+    <t>Richtlinie zur Schwachstellen-Offenlegung, Schwachstellenaufzeichnungen, Nachweise Patch-Management, Penetrationstestberichte, Zertifizierungen der Systeme</t>
+  </si>
+  <si>
+    <t>Die Entwicklung der Rechtsverordnung beobachten. Schwerpunkt liegt zur Zeit bei 5G und Software-Produkten.</t>
+  </si>
+  <si>
+    <t>Meldung von Sicherheitsvorfällen &amp; Benachrichtigungen</t>
+  </si>
+  <si>
+    <t>3.2.17</t>
+  </si>
+  <si>
+    <t>Meldung/Reporting</t>
+  </si>
+  <si>
+    <t>Erhebliche Sicherheitsvorfälle sind über die gemeinsame Meldestelle zu melden: (1) frühe Erstmeldung spätestens binnen 24 Stunden nach Kenntniserlangung, (2) Meldung spätestens binnen 72 Stunden mit Bestätigung/Aktualisierung und erster Bewertung (inkl. Schweregrad/Auswirkungen und ggf. Kompromittierungsindikatoren), (3) auf Ersuchen Zwischenmeldungen, (4) Abschlussmeldung spätestens einen Monat nach der 72-Stunden-Meldung (bei andauerndem Vorfall zunächst Fortschrittsmeldung). Die Pflichten gelten frühestens ab Einrichtung des Meldewegs.
 DE: BSIG §32 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vorfallberichte, Melde-/Benachrichtigungsvorlagen, Zeitlinien, Nachweise der Meldung an Behörde/CSIRT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interne Klärung, welche Vorfälle als "erheblich" gelten - damit bei einem tatsächlichen Vorfall keine Verzögerung entsteht;
+    <t>#Reporting</t>
+  </si>
+  <si>
+    <t>Vorfallberichte, Melde-/Benachrichtigungsvorlagen, Zeitlinien, Nachweise der Meldung an Behörde/CSIRT</t>
+  </si>
+  <si>
+    <t>Interne Klärung, welche Vorfälle als "erheblich" gelten - damit bei einem tatsächlichen Vorfall keine Verzögerung entsteht;
 Prüfung, ob es eine allgemeine Übersicht oder Richtlinie für erhebliche Sicherheitsvorfälle gibt (z.B. vom BSI)
 Zeitpunkt der Kenntniserlangung dokumentieren ("innerhalb der Arbeitszeit")</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Im Fall eines erheblichen Sicherheitsvorfalls kann das BSI anordnen, dass Empfänger der Dienste unverzüglich über den Vorfall zu unterrichten sind, wenn die Erbringung des jeweiligen Dienstes beeinträchtigt sein könnte (ggf. auch per Veröffentlichung). Für bestimmte Sektoren bestehen zudem Pflichten, potenziell betroffene Empfänger über erhebliche Cyberbedrohungen sowie geeignete Abwehr- oder Abhilfemaßnahmen zu informieren.
+    <t>3.2.18</t>
+  </si>
+  <si>
+    <t>Im Fall eines erheblichen Sicherheitsvorfalls kann das BSI anordnen, dass Empfänger der Dienste unverzüglich über den Vorfall zu unterrichten sind, wenn die Erbringung des jeweiligen Dienstes beeinträchtigt sein könnte (ggf. auch per Veröffentlichung). Für bestimmte Sektoren bestehen zudem Pflichten, potenziell betroffene Empfänger über erhebliche Cyberbedrohungen sowie geeignete Abwehr- oder Abhilfemaßnahmen zu informieren.
 DE: BSIG §35 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Vorfallmanagement ISO 27001/27002: A.6.1.3 Contact with authorities; A.5.24 - A.5.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kunden-, Behörden-, Versicherungs- und Lieferantendaten so vorhalten, dass sie auch bei einem Ransomware-Angriff abrufbar sind.
+    <t>#Vorfallmanagement ISO 27001/27002: A.6.1.3 Contact with authorities; A.5.24 - A.5.27</t>
+  </si>
+  <si>
+    <t>Kunden-, Behörden-, Versicherungs- und Lieferantendaten so vorhalten, dass sie auch bei einem Ransomware-Angriff abrufbar sind.
 Prozesse vorsehen, die eine Information an interessierte Kreise ermöglichen.</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Das BSI kann Warnungen und Informationen an die Öffentlichkeit oder an betroffene Kreise richten (z. B. zu Schwachstellen, Schadprogrammen, Datenverlust oder unbefugtem Datenzugriff sowie zu sicherheitsrelevanten IT-Eigenschaften) und Sicherheitsmaßnahmen bzw. den Einsatz bestimmter Sicherheitsprodukte empfehlen. Hersteller betroffener Produkte sind grundsätzlich vorab zu informieren; Warnungen werden bei Wegfall der Voraussetzungen regelmäßig überprüft.
+    <t>2.3.1</t>
+  </si>
+  <si>
+    <t>Das BSI kann Warnungen und Informationen an die Öffentlichkeit oder an betroffene Kreise richten (z. B. zu Schwachstellen, Schadprogrammen, Datenverlust oder unbefugtem Datenzugriff sowie zu sicherheitsrelevanten IT-Eigenschaften) und Sicherheitsmaßnahmen bzw. den Einsatz bestimmter Sicherheitsprodukte empfehlen. Hersteller betroffener Produkte sind grundsätzlich vorab zu informieren; Warnungen werden bei Wegfall der Voraussetzungen regelmäßig überprüft.
 DE: BSIG §13 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Vorfallmanagement ISO 27001/27002: A.5.5 Beziehungen zu den Behörden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geschäftsführung über die Möglichkeiten des BSI in Kenntnis setzen.
+    <t>#Vorfallmanagement ISO 27001/27002: A.5.5 Beziehungen zu den Behörden</t>
+  </si>
+  <si>
+    <t>Geschäftsführung über die Möglichkeiten des BSI in Kenntnis setzen.
 Meldung von BSI und Dritten ermöglichen und Reaktionen garantieren. Ggf. über security.txt auf Webseite.
 Kommunikation mit den Behörden etablieren und regelmäßig Informationen über diese Kanäle abrufen.</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Das BSI kann Abfragen an den Schnittstellen öffentlich erreichbarer informationstechnischer Systeme zu öffentlichen Telekommunikationsnetzen durchführen, um bekannte Schwachstellen oder andere Sicherheitsrisiken zu detektieren – auch auf Ersuchen von Einrichtungen. Wird ein Risiko erkannt, informiert das BSI die Verantwortlichen unverzüglich und weist auf bestehende Möglichkeiten zur Abhilfe hin.
+    <t>2.3.2</t>
+  </si>
+  <si>
+    <t>Das BSI kann Abfragen an den Schnittstellen öffentlich erreichbarer informationstechnischer Systeme zu öffentlichen Telekommunikationsnetzen durchführen, um bekannte Schwachstellen oder andere Sicherheitsrisiken zu detektieren – auch auf Ersuchen von Einrichtungen. Wird ein Risiko erkannt, informiert das BSI die Verantwortlichen unverzüglich und weist auf bestehende Möglichkeiten zur Abhilfe hin.
 DE: BSIG §15 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Risikomanagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontinuierliches Updaten hinsichtlich IT-Sicherheits-relevanter Produkte/Systeme/Dienste, die öffentlich erreichbar sind. 
+    <t>#Risikomanagement</t>
+  </si>
+  <si>
+    <t>Kontinuierliches Updaten hinsichtlich IT-Sicherheits-relevanter Produkte/Systeme/Dienste, die öffentlich erreichbar sind. 
 Klärung mit Dienstleistern, ob diese für gemanagte Services auch kontinuierliche Updates durchführen.
 Regelmäßige Prüfung, ob die öffentlich erreichbaren Systeme auch notwendigerweise erreichbar sein müssen.
 Penetration Tests bzw. Schwachstellenprüfung bei neuen Produkten/Diensten, die relevant für die Geschäftsprozesse sind und/oder mind. jährliche Prüfung des externen Angreifbarkeit (Schwachstellen und Konfigurationsfehler in öffentlich erreichbaren Systemen) sowie anlassbezogen. -&gt; "External Attack Surcface"
@@ -1011,58 +1167,59 @@
 Warnung bei OT-Schwachstellenprüfung: Aktive Schwachstellenscans in der Produktionsumgebung können zu einem (dauerhaften) Ausfall der OT-Systeme führen und sollten nur nach Absprache mit den Produktionsverantwortlichen und den Lieferanten durchgeführt werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aufsicht &amp; Durchsetzung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schwachstellenmanagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Das BSI betreibt eine Online-Plattform zum Informationsaustausch mit wichtigen Einrichtungen, besonders wichtigen Einrichtungen und Einrichtungen der Bundesverwaltung. Der Austausch umfasst u. a. Cyberbedrohungen, Schwachstellen, Beinahevorfälle und IT-Sicherheitsmaßnahmen; Hersteller, Lieferanten oder Dienstleister können einbezogen werden.
+    <t>Aufsicht &amp; Durchsetzung</t>
+  </si>
+  <si>
+    <t>2.3.3</t>
+  </si>
+  <si>
+    <t>Schwachstellenmanagement</t>
+  </si>
+  <si>
+    <t>Das BSI betreibt eine Online-Plattform zum Informationsaustausch mit wichtigen Einrichtungen, besonders wichtigen Einrichtungen und Einrichtungen der Bundesverwaltung. Der Austausch umfasst u. a. Cyberbedrohungen, Schwachstellen, Beinahevorfälle und IT-Sicherheitsmaßnahmen; Hersteller, Lieferanten oder Dienstleister können einbezogen werden.
 DE: BSIG §6 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Schwachstellenmanagement ISO 27001/27002: All controls with operational capability #Bedrohungs_und_Schwachstellenmanagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entwicklung beobachten und entsprechend beim BSI nach Freischaltung des Portals registrieren.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korrekturmaßnahmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechtfertigen Tatsachen die Annahme, dass eine wichtige Einrichtung Verpflichtungen nach BSIG §30, §32 oder §38 nicht oder nicht richtig umsetzt, kann das BSI die Einhaltung überprüfen und Aufsichts-/Durchsetzungsmaßnahmen ergreifen (Maßnahmen nach §61). Gegenüber besonders wichtigen Einrichtungen kann das BSI u. a. Audits/Prüfungen/Zertifizierungen anordnen, Nachweise verlangen und bei Mängeln konkrete Abhilfemaßnahmen sowie Mängelbeseitigungspläne anordnen.
+    <t>#Schwachstellenmanagement ISO 27001/27002: All controls with operational capability #Bedrohungs_und_Schwachstellenmanagement</t>
+  </si>
+  <si>
+    <t>Entwicklung beobachten und entsprechend beim BSI nach Freischaltung des Portals registrieren.</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Korrekturmaßnahmen</t>
+  </si>
+  <si>
+    <t>Rechtfertigen Tatsachen die Annahme, dass eine wichtige Einrichtung Verpflichtungen nach BSIG §30, §32 oder §38 nicht oder nicht richtig umsetzt, kann das BSI die Einhaltung überprüfen und Aufsichts-/Durchsetzungsmaßnahmen ergreifen (Maßnahmen nach §61). Gegenüber besonders wichtigen Einrichtungen kann das BSI u. a. Audits/Prüfungen/Zertifizierungen anordnen, Nachweise verlangen und bei Mängeln konkrete Abhilfemaßnahmen sowie Mängelbeseitigungspläne anordnen.
 DE: BSIG §62 i. V. m. §61 (BGBl. I 2025 Nr. 301)</t>
   </si>
   <si>
-    <t xml:space="preserve">#Korrekturmaßnahmen ISO 27001/27002: Kapitel 10 „Verbesserung“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dokumentation der Maßnahmen (in dieser Excel-Tabelle genügt).
+    <t>#Korrekturmaßnahmen ISO 27001/27002: Kapitel 10 „Verbesserung“</t>
+  </si>
+  <si>
+    <t>Dokumentation der Maßnahmen (in dieser Excel-Tabelle genügt).
 Vorhalten entsprechender Nachweise (z.B. Schulung, Zertifikate, Auditberichte).
 Regelmäßige Überprüfung der Maßnahmen sicherstellen. 
 Sollte bereits ein ISMS in Betrieb sein, sollten die Maßnahmen im ISMS dokumentiert werden. Ggf. ISO 9001 Management-System nutzen, falls vorhanden.</t>
+  </si>
+  <si>
+    <t>externe Risikomeldungen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;- &quot;_€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0&quot; €&quot;_-;\-* #,##0&quot; €&quot;_-;_-* &quot;- €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0\ %"/>
-    <numFmt numFmtId="170" formatCode="@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;- &quot;_€_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0&quot; €&quot;_-;\-* #,##0&quot; €&quot;_-;_-* &quot;- €&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1072,22 +1229,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1098,15 +1239,20 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1126,114 +1272,70 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="26">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Comma" xfId="20"/>
-    <cellStyle name="Comma [0]" xfId="21"/>
-    <cellStyle name="Currency" xfId="22"/>
-    <cellStyle name="Currency [0]" xfId="23"/>
-    <cellStyle name="Normal" xfId="24"/>
-    <cellStyle name="Percent" xfId="25"/>
+  <cellStyles count="7">
+    <cellStyle name="Comma" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Comma [0]" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Currency" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Currency [0]" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Percent" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1292,47 +1394,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1340,14 +1458,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1410,7 +1528,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1428,38 +1546,37 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K1048576"/>
-  <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="37.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="38.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="28.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="57.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20.85"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="1" width="11.43"/>
+    <col min="1" max="1" width="11.5" style="1"/>
+    <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="62.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="38.83203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="28.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="57.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1494,7 +1611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="92.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="112" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1529,7 +1646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="180.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11" ht="180" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -1564,7 +1681,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="92.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:11" ht="128" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -1599,7 +1716,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="100.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11" ht="100.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1634,7 +1751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="216.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:11" ht="288" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -1669,7 +1786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -1704,7 +1821,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="152.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:11" ht="192" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -1739,7 +1856,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="92.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:11" ht="128" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1774,7 +1891,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1809,7 +1926,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1844,7 +1961,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -1879,7 +1996,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1914,7 +2031,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1949,7 +2066,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
@@ -1984,7 +2101,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
@@ -2019,7 +2136,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
@@ -2054,7 +2171,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
@@ -2089,7 +2206,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -2124,7 +2241,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
@@ -2159,7 +2276,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
@@ -2194,7 +2311,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
@@ -2229,7 +2346,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="125.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:11" ht="176" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
@@ -2264,7 +2381,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="103.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:11" ht="144" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>11</v>
       </c>
@@ -2299,7 +2416,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="117.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:11" ht="117.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2334,7 +2451,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="257.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:11" ht="335" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>11</v>
       </c>
@@ -2348,7 +2465,7 @@
         <v>152</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>153</v>
@@ -2369,7 +2486,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="92.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:11" ht="128" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>11</v>
       </c>
@@ -2404,7 +2521,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="114.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:11" ht="160" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>11</v>
       </c>
@@ -2439,15 +2556,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>